--- a/data/trans_orig/P33B4_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P33B4_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que se siente cansado cuando despierta por la mañana en 2023</t>
+          <t>Población según la frecuencia con la que se siente cansado cuando despierta por la mañana en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20261</t>
+          <t>19372</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41109</t>
+          <t>40501</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30841</t>
+          <t>30210</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51770</t>
+          <t>51655</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54584</t>
+          <t>55424</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84786</t>
+          <t>84551</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15639</t>
+          <t>15124</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34750</t>
+          <t>33603</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28107</t>
+          <t>27864</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47771</t>
+          <t>47897</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47973</t>
+          <t>48400</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74070</t>
+          <t>74171</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>72681</t>
+          <t>72924</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>107511</t>
+          <t>109254</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>72238</t>
+          <t>72441</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>100729</t>
+          <t>99013</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>153395</t>
+          <t>154225</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>199718</t>
+          <t>200567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,05%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>343504</t>
+          <t>342329</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>382862</t>
+          <t>384084</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,82 +1084,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>67,76%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>76,02%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>284118</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>266872</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>301264</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>63,49%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>59,64%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>67,33%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>807</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>647752</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>619767</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>673797</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
           <t>67,99%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>75,78%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>417</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>284118</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>265001</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>301290</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>63,49%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>59,22%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>67,33%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>807</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>647752</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>618067</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>675024</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>67,99%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,73%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16279</t>
+          <t>16708</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36048</t>
+          <t>35926</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26818</t>
+          <t>26310</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>47063</t>
+          <t>47637</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>47653</t>
+          <t>48332</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>74608</t>
+          <t>75734</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,08%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21348</t>
+          <t>20980</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44113</t>
+          <t>43090</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30607</t>
+          <t>30871</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50469</t>
+          <t>50684</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57073</t>
+          <t>57319</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86527</t>
+          <t>86667</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75685</t>
+          <t>72755</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>108162</t>
+          <t>107335</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71590</t>
+          <t>71560</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>98227</t>
+          <t>97922</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>152303</t>
+          <t>151438</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>194244</t>
+          <t>194051</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,27%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>284579</t>
+          <t>286300</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>324072</t>
+          <t>326056</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>207619</t>
+          <t>207366</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>239414</t>
+          <t>239638</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>503548</t>
+          <t>503712</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>555023</t>
+          <t>556146</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,7%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14859</t>
+          <t>15164</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>71503</t>
+          <t>74191</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17737</t>
+          <t>17401</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31751</t>
+          <t>31333</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>26909</t>
+          <t>29867</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>99893</t>
+          <t>98676</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,83%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13362</t>
+          <t>15422</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>68533</t>
+          <t>69429</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13452</t>
+          <t>12739</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25922</t>
+          <t>25687</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>22878</t>
+          <t>20986</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>85603</t>
+          <t>86269</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26076</t>
+          <t>30446</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>129700</t>
+          <t>132595</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31248</t>
+          <t>31031</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>49870</t>
+          <t>49564</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44178</t>
+          <t>52670</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>174829</t>
+          <t>172942</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>410178</t>
+          <t>405214</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>606210</t>
+          <t>605594</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>73740</t>
+          <t>74437</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>94967</t>
+          <t>95138</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>483607</t>
+          <t>486671</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>735518</t>
+          <t>722143</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>86,57%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>71676</t>
+          <t>73058</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>108614</t>
+          <t>108214</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42098</t>
+          <t>43510</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>115371</t>
+          <t>112479</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>122128</t>
+          <t>112553</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>205434</t>
+          <t>202495</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,06%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>57794</t>
+          <t>57704</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>89431</t>
+          <t>88263</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>41427</t>
+          <t>37087</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>107446</t>
+          <t>106252</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>107379</t>
+          <t>98959</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>179449</t>
+          <t>178479</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>141570</t>
+          <t>144205</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>194525</t>
+          <t>198970</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>77810</t>
+          <t>76353</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>196675</t>
+          <t>194264</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>235113</t>
+          <t>204656</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>367320</t>
+          <t>367020</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,24%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>673242</t>
+          <t>674489</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>737956</t>
+          <t>738226</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>570787</t>
+          <t>574327</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>816628</t>
+          <t>814673</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1284425</t>
+          <t>1288109</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1557482</t>
+          <t>1612872</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>80,14%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>25751</t>
+          <t>26018</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>46967</t>
+          <t>48755</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>81943</t>
+          <t>84612</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>133459</t>
+          <t>133857</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>119282</t>
+          <t>114857</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>169254</t>
+          <t>169715</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,93%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22233</t>
+          <t>20609</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>46901</t>
+          <t>44798</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>71358</t>
+          <t>73217</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>119418</t>
+          <t>121940</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>102845</t>
+          <t>103226</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>153197</t>
+          <t>151109</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,51%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>65624</t>
+          <t>65288</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>99316</t>
+          <t>99012</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>118903</t>
+          <t>124550</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>190875</t>
+          <t>193262</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>199859</t>
+          <t>201341</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>274748</t>
+          <t>275803</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,01%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>303642</t>
+          <t>303620</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>346141</t>
+          <t>348120</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>414202</t>
+          <t>409172</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>573852</t>
+          <t>557552</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>744438</t>
+          <t>742739</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>894257</t>
+          <t>890220</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>67,8%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2737</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>23580</t>
+          <t>26156</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>78111</t>
+          <t>79767</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>108580</t>
+          <t>109086</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>85199</t>
+          <t>85176</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>120168</t>
+          <t>121337</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3095</t>
+          <t>3821</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>22131</t>
+          <t>23659</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>65972</t>
+          <t>65081</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>95604</t>
+          <t>96362</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>71673</t>
+          <t>72228</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>109907</t>
+          <t>108409</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>7128</t>
+          <t>6716</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>34105</t>
+          <t>31678</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>144127</t>
+          <t>143420</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>182027</t>
+          <t>181496</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>156104</t>
+          <t>154160</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>202112</t>
+          <t>200258</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,0%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>185934</t>
+          <t>184556</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>221345</t>
+          <t>219407</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>402774</t>
+          <t>399873</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>454533</t>
+          <t>449423</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>599748</t>
+          <t>598167</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>663195</t>
+          <t>666426</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>66,56%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>173794</t>
+          <t>179433</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>261333</t>
+          <t>265961</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>319203</t>
+          <t>312620</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>431171</t>
+          <t>433625</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>530122</t>
+          <t>534764</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>677550</t>
+          <t>677248</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>156452</t>
+          <t>161845</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>238954</t>
+          <t>239140</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>283520</t>
+          <t>288292</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>388914</t>
+          <t>392318</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>480294</t>
+          <t>485120</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>617409</t>
+          <t>617316</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>408533</t>
+          <t>406817</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>583718</t>
+          <t>578294</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>565802</t>
+          <t>564872</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>747692</t>
+          <t>753241</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1057444</t>
+          <t>1049040</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1306502</t>
+          <t>1303936</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,77%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2323349</t>
+          <t>2322280</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2633993</t>
+          <t>2607200</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2028932</t>
+          <t>2021950</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2405509</t>
+          <t>2418722</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,17 +4548,17 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>4567058</t>
+          <t>4567059</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4390934</t>
+          <t>4394578</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4861742</t>
+          <t>4874823</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>70,17%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33B4_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P33B4_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28585</t>
+          <t>30807</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19372</t>
+          <t>21312</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40501</t>
+          <t>42308</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>40404</t>
+          <t>43498</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30210</t>
+          <t>33292</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51655</t>
+          <t>55626</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>68989</t>
+          <t>74305</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55424</t>
+          <t>60385</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84551</t>
+          <t>90941</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23046</t>
+          <t>27070</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15124</t>
+          <t>18065</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33603</t>
+          <t>39509</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>37021</t>
+          <t>44789</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27864</t>
+          <t>34558</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47897</t>
+          <t>57811</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>60068</t>
+          <t>71859</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48400</t>
+          <t>57530</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74171</t>
+          <t>90002</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>89946</t>
+          <t>96606</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>72924</t>
+          <t>77657</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>109254</t>
+          <t>114052</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>85924</t>
+          <t>93884</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>72441</t>
+          <t>81502</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>99013</t>
+          <t>110263</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>175870</t>
+          <t>190490</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>154225</t>
+          <t>168544</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>200567</t>
+          <t>214687</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,66%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>363634</t>
+          <t>396135</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>342329</t>
+          <t>375622</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>384084</t>
+          <t>418177</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>284118</t>
+          <t>306240</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>266872</t>
+          <t>288970</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>301264</t>
+          <t>324573</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>647752</t>
+          <t>702376</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>619767</t>
+          <t>675181</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>673797</t>
+          <t>733724</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>70,62%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24511</t>
+          <t>27061</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16708</t>
+          <t>18502</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35926</t>
+          <t>39905</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>35547</t>
+          <t>39952</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26310</t>
+          <t>31016</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>47637</t>
+          <t>53146</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>60057</t>
+          <t>67014</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>48332</t>
+          <t>53648</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>75734</t>
+          <t>83863</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>30574</t>
+          <t>31133</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20980</t>
+          <t>21140</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43090</t>
+          <t>44548</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>39742</t>
+          <t>44179</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30871</t>
+          <t>34175</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50684</t>
+          <t>58208</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>70316</t>
+          <t>75313</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57319</t>
+          <t>60991</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86667</t>
+          <t>91767</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>89473</t>
+          <t>96507</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72755</t>
+          <t>78975</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>107335</t>
+          <t>114625</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>83691</t>
+          <t>92717</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71560</t>
+          <t>78520</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>97922</t>
+          <t>107071</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>173164</t>
+          <t>189225</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>151438</t>
+          <t>167696</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>194051</t>
+          <t>212936</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>306687</t>
+          <t>327522</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>286300</t>
+          <t>305096</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>326056</t>
+          <t>347152</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>223601</t>
+          <t>246294</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>207366</t>
+          <t>227605</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>239638</t>
+          <t>264183</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>530287</t>
+          <t>573816</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>503712</t>
+          <t>547246</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>556146</t>
+          <t>600928</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,37%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>451244</t>
+          <t>482224</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>451244</t>
+          <t>482224</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>451244</t>
+          <t>482224</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>833824</t>
+          <t>905367</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>833824</t>
+          <t>905367</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>833824</t>
+          <t>905367</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>41898</t>
+          <t>44780</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15164</t>
+          <t>33928</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>74191</t>
+          <t>59712</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>23783</t>
+          <t>27291</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17401</t>
+          <t>20038</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31333</t>
+          <t>35562</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>65682</t>
+          <t>72071</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29867</t>
+          <t>57729</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>98676</t>
+          <t>87696</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>13,32%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>38945</t>
+          <t>41887</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15422</t>
+          <t>29846</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>69429</t>
+          <t>56362</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18607</t>
+          <t>20133</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12739</t>
+          <t>14415</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25687</t>
+          <t>27129</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>57552</t>
+          <t>62020</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>20986</t>
+          <t>49015</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>86269</t>
+          <t>78765</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>78074</t>
+          <t>88138</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30446</t>
+          <t>73293</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>132595</t>
+          <t>106490</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>39907</t>
+          <t>42955</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31031</t>
+          <t>33857</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>49564</t>
+          <t>54394</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>117980</t>
+          <t>131093</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52670</t>
+          <t>112449</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>172942</t>
+          <t>152455</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>508331</t>
+          <t>295828</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>405214</t>
+          <t>272160</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>605594</t>
+          <t>315355</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>84614</t>
+          <t>97118</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>74437</t>
+          <t>86105</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>95138</t>
+          <t>108452</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>592944</t>
+          <t>392945</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>486671</t>
+          <t>366576</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>722143</t>
+          <t>415297</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>63,1%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>667248</t>
+          <t>470633</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>667248</t>
+          <t>470633</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>667248</t>
+          <t>470633</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>834158</t>
+          <t>658130</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>834158</t>
+          <t>658130</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>834158</t>
+          <t>658130</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>88703</t>
+          <t>98012</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>73058</t>
+          <t>78744</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>108214</t>
+          <t>120021</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>84187</t>
+          <t>94774</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>43510</t>
+          <t>78589</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>112479</t>
+          <t>112123</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>172891</t>
+          <t>192786</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>112553</t>
+          <t>167537</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>202495</t>
+          <t>219523</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>72381</t>
+          <t>77875</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>57704</t>
+          <t>63316</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>88263</t>
+          <t>95728</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>79314</t>
+          <t>88946</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>37087</t>
+          <t>74584</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>106252</t>
+          <t>104704</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>151695</t>
+          <t>166821</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>98959</t>
+          <t>146620</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>178479</t>
+          <t>193827</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>166780</t>
+          <t>181178</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>144205</t>
+          <t>156865</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>198970</t>
+          <t>205270</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>149015</t>
+          <t>166809</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>76353</t>
+          <t>149951</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>194264</t>
+          <t>188081</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>315794</t>
+          <t>347987</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>204656</t>
+          <t>317398</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>367020</t>
+          <t>379056</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>19,02%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>706955</t>
+          <t>774779</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>674489</t>
+          <t>739187</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>738226</t>
+          <t>806568</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>665171</t>
+          <t>510267</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>574327</t>
+          <t>485627</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>814673</t>
+          <t>534371</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1372125</t>
+          <t>1285045</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1288109</t>
+          <t>1243113</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1612872</t>
+          <t>1324418</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>66,47%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>977687</t>
+          <t>860796</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>977687</t>
+          <t>860796</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>977687</t>
+          <t>860796</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2012505</t>
+          <t>1992639</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2012505</t>
+          <t>1992639</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2012505</t>
+          <t>1992639</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>35369</t>
+          <t>43047</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>26018</t>
+          <t>31992</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>48755</t>
+          <t>57792</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>111480</t>
+          <t>126934</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>84612</t>
+          <t>110915</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>133857</t>
+          <t>145830</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>146849</t>
+          <t>169981</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>114857</t>
+          <t>147956</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>169715</t>
+          <t>192043</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>31154</t>
+          <t>34293</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20609</t>
+          <t>23734</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>44798</t>
+          <t>50126</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>97480</t>
+          <t>102360</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>73217</t>
+          <t>87965</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>121940</t>
+          <t>119516</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>128633</t>
+          <t>136653</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>103226</t>
+          <t>118933</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>151109</t>
+          <t>158748</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,36%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>80548</t>
+          <t>94618</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>65288</t>
+          <t>77090</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>99012</t>
+          <t>114398</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>165466</t>
+          <t>184684</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>124550</t>
+          <t>165523</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>193262</t>
+          <t>205099</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>246014</t>
+          <t>279302</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>201341</t>
+          <t>253049</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>275803</t>
+          <t>307547</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>22,01%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>326945</t>
+          <t>394923</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>303620</t>
+          <t>369995</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>348120</t>
+          <t>416644</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>464570</t>
+          <t>416150</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>409172</t>
+          <t>392594</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>557552</t>
+          <t>439788</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>791516</t>
+          <t>811073</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>742739</t>
+          <t>776254</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>890220</t>
+          <t>846086</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>60,56%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1313012</t>
+          <t>1397009</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1313012</t>
+          <t>1397009</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1313012</t>
+          <t>1397009</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>8557</t>
+          <t>7679</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2809</t>
+          <t>2461</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26156</t>
+          <t>22165</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>93709</t>
+          <t>104856</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>79767</t>
+          <t>88069</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>109086</t>
+          <t>119061</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>102266</t>
+          <t>112536</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>85176</t>
+          <t>95325</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>121337</t>
+          <t>131870</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,2%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>9515</t>
+          <t>12561</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3821</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>23659</t>
+          <t>26037</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>79108</t>
+          <t>87035</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>65081</t>
+          <t>72927</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>96362</t>
+          <t>104409</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>88624</t>
+          <t>99597</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>72228</t>
+          <t>83193</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>108409</t>
+          <t>120181</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>16128</t>
+          <t>15645</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>6716</t>
+          <t>6892</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>31678</t>
+          <t>29995</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>161780</t>
+          <t>177185</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>143420</t>
+          <t>158140</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>181496</t>
+          <t>198554</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>177907</t>
+          <t>192830</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>154160</t>
+          <t>170160</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>200258</t>
+          <t>217293</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,11%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>206307</t>
+          <t>201342</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>184556</t>
+          <t>182595</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>219407</t>
+          <t>214304</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>426127</t>
+          <t>474463</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>399873</t>
+          <t>447781</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>449423</t>
+          <t>502943</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>632434</t>
+          <t>675806</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>598167</t>
+          <t>640884</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>666426</t>
+          <t>706290</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>65,35%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>760724</t>
+          <t>843540</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>760724</t>
+          <t>843540</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>760724</t>
+          <t>843540</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1001231</t>
+          <t>1080768</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1001231</t>
+          <t>1080768</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1001231</t>
+          <t>1080768</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>227624</t>
+          <t>251386</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>179433</t>
+          <t>221851</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>265961</t>
+          <t>284127</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>389110</t>
+          <t>437305</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>312620</t>
+          <t>405572</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>433625</t>
+          <t>474196</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>616734</t>
+          <t>688692</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>534764</t>
+          <t>645083</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>677248</t>
+          <t>737844</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>205615</t>
+          <t>224819</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>161845</t>
+          <t>197574</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>239140</t>
+          <t>259435</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>351273</t>
+          <t>387443</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>288292</t>
+          <t>356663</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>392318</t>
+          <t>424732</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>556888</t>
+          <t>612263</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>485120</t>
+          <t>565838</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>617316</t>
+          <t>660653</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>520949</t>
+          <t>572692</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>406817</t>
+          <t>527315</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>578294</t>
+          <t>619228</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>685781</t>
+          <t>758234</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>564872</t>
+          <t>717863</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>753241</t>
+          <t>799848</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>1206730</t>
+          <t>1330926</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1049040</t>
+          <t>1264563</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1303936</t>
+          <t>1387694</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>19,62%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2418859</t>
+          <t>2390530</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2322280</t>
+          <t>2335500</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2607200</t>
+          <t>2451832</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>2148201</t>
+          <t>2050532</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2021950</t>
+          <t>1996504</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2418722</t>
+          <t>2101947</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>4567059</t>
+          <t>4441062</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4394578</t>
+          <t>4361855</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4874823</t>
+          <t>4519690</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>63,9%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3373046</t>
+          <t>3439428</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3373046</t>
+          <t>3439428</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3373046</t>
+          <t>3439428</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3574365</t>
+          <t>3633515</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3574365</t>
+          <t>3633515</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3574365</t>
+          <t>3633515</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>6947410</t>
+          <t>7072943</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6947410</t>
+          <t>7072943</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6947410</t>
+          <t>7072943</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
